--- a/artfynd/A 33440-2026 artfynd.xlsx
+++ b/artfynd/A 33440-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136100274</v>
       </c>
       <c r="B2" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136100281</v>
       </c>
       <c r="B3" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136100293</v>
       </c>
       <c r="B4" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136100271</v>
       </c>
       <c r="B10" t="n">
-        <v>92281</v>
+        <v>92284</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136100284</v>
       </c>
       <c r="B11" t="n">
-        <v>92281</v>
+        <v>92284</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136100289</v>
       </c>
       <c r="B12" t="n">
-        <v>92281</v>
+        <v>92284</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136100301</v>
       </c>
       <c r="B13" t="n">
-        <v>92281</v>
+        <v>92284</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136100424</v>
       </c>
       <c r="B14" t="n">
-        <v>92281</v>
+        <v>92284</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136100280</v>
       </c>
       <c r="B15" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136100303</v>
       </c>
       <c r="B16" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136100326</v>
       </c>
       <c r="B17" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136100427</v>
       </c>
       <c r="B18" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136100286</v>
       </c>
       <c r="B19" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136100292</v>
       </c>
       <c r="B20" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136100295</v>
       </c>
       <c r="B21" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136100313</v>
       </c>
       <c r="B22" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136100323</v>
       </c>
       <c r="B23" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136100419</v>
       </c>
       <c r="B24" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136100422</v>
       </c>
       <c r="B25" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>136100269</v>
       </c>
       <c r="B26" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>136100306</v>
       </c>
       <c r="B27" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>136100312</v>
       </c>
       <c r="B28" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>136100320</v>
       </c>
       <c r="B29" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>136100331</v>
       </c>
       <c r="B30" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>136100332</v>
       </c>
       <c r="B31" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>136100333</v>
       </c>
       <c r="B32" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>136100335</v>
       </c>
       <c r="B33" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>136100425</v>
       </c>
       <c r="B34" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>136100432</v>
       </c>
       <c r="B35" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>136100272</v>
       </c>
       <c r="B36" t="n">
-        <v>93404</v>
+        <v>93407</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>136100322</v>
       </c>
       <c r="B37" t="n">
-        <v>93404</v>
+        <v>93407</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>136100325</v>
       </c>
       <c r="B38" t="n">
-        <v>93404</v>
+        <v>93407</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>136100291</v>
       </c>
       <c r="B39" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>136100305</v>
       </c>
       <c r="B40" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>136100416</v>
       </c>
       <c r="B66" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 33440-2026 artfynd.xlsx
+++ b/artfynd/A 33440-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136100274</v>
       </c>
       <c r="B2" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136100281</v>
       </c>
       <c r="B3" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136100293</v>
       </c>
       <c r="B4" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136100271</v>
       </c>
       <c r="B10" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136100284</v>
       </c>
       <c r="B11" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136100289</v>
       </c>
       <c r="B12" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136100301</v>
       </c>
       <c r="B13" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136100424</v>
       </c>
       <c r="B14" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136100286</v>
       </c>
       <c r="B19" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136100292</v>
       </c>
       <c r="B20" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136100295</v>
       </c>
       <c r="B21" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136100313</v>
       </c>
       <c r="B22" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136100323</v>
       </c>
       <c r="B23" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136100419</v>
       </c>
       <c r="B24" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136100422</v>
       </c>
       <c r="B25" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>136100269</v>
       </c>
       <c r="B26" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>136100306</v>
       </c>
       <c r="B27" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>136100312</v>
       </c>
       <c r="B28" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>136100320</v>
       </c>
       <c r="B29" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>136100331</v>
       </c>
       <c r="B30" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>136100332</v>
       </c>
       <c r="B31" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>136100333</v>
       </c>
       <c r="B32" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>136100335</v>
       </c>
       <c r="B33" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>136100425</v>
       </c>
       <c r="B34" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>136100432</v>
       </c>
       <c r="B35" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>136100272</v>
       </c>
       <c r="B36" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>136100322</v>
       </c>
       <c r="B37" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>136100325</v>
       </c>
       <c r="B38" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>136100291</v>
       </c>
       <c r="B39" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>136100305</v>
       </c>
       <c r="B40" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>136100416</v>
       </c>
       <c r="B66" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
